--- a/data/performance/daily/signal_list_2026-05-26.xlsx
+++ b/data/performance/daily/signal_list_2026-05-26.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="D5" t="n">
         <v>1270</v>
@@ -553,10 +553,10 @@
         <v>1345</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-4.87</v>
+        <v>-5.22</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" t="n">
         <v>156</v>
@@ -669,10 +669,10 @@
         <v>159</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.63</v>
+        <v>1.27</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.27</v>
+        <v>-0.64</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2490</v>
+        <v>2450</v>
       </c>
       <c r="D10" t="n">
         <v>2460</v>
@@ -753,14 +753,14 @@
         <v>2500</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4</v>
+        <v>2.04</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.41</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D11" t="n">
         <v>1135</v>
@@ -795,10 +795,10 @@
         <v>1145</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.09</v>
+        <v>5.05</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.18</v>
+        <v>4.13</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>64</v>
@@ -837,10 +837,10 @@
         <v>85</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.41</v>
+        <v>21.43</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-22.89</v>
+        <v>-8.57</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>760</v>
+        <v>830</v>
       </c>
       <c r="D13" t="n">
         <v>710</v>
@@ -879,10 +879,10 @@
         <v>770</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.32</v>
+        <v>-7.23</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-6.58</v>
+        <v>-14.46</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13525</v>
+        <v>15350</v>
       </c>
       <c r="D14" t="n">
         <v>13550</v>
@@ -921,14 +921,14 @@
         <v>14100</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-11.73</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D16" t="n">
         <v>282</v>
@@ -1005,10 +1005,10 @@
         <v>282</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.22</v>
+        <v>6.02</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.22</v>
+        <v>6.02</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D17" t="n">
         <v>106</v>
@@ -1047,10 +1047,10 @@
         <v>112</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.67</v>
+        <v>1.82</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.93</v>
+        <v>-3.64</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
         <v>71</v>
@@ -1131,10 +1131,10 @@
         <v>82</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.81</v>
+        <v>7.89</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.05</v>
+        <v>-6.58</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D21" t="n">
         <v>500</v>
@@ -1215,10 +1215,10 @@
         <v>515</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.91</v>
+        <v>-0.99</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 42.9%  (9W / 12L of 21 evaluated, 1 pending)</t>
+          <t>Win Rate: 38.1%  (8W / 13L of 21 evaluated, 1 pending)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="D6" t="n">
         <v>1270</v>
@@ -1391,10 +1391,10 @@
         <v>1345</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.87</v>
+        <v>-5.22</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5825</v>
+        <v>5800</v>
       </c>
       <c r="D10" t="n">
         <v>5850</v>
@@ -1549,10 +1549,10 @@
         <v>5850</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4100</v>
+        <v>4330</v>
       </c>
       <c r="D11" t="n">
         <v>4100</v>
@@ -1591,10 +1591,10 @@
         <v>4100</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>-5.31</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>-5.31</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1485</v>
+        <v>1440</v>
       </c>
       <c r="D12" t="n">
         <v>1500</v>
@@ -1633,10 +1633,10 @@
         <v>1505</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.35</v>
+        <v>4.51</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.01</v>
+        <v>4.17</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2490</v>
+        <v>2450</v>
       </c>
       <c r="D13" t="n">
         <v>2460</v>
@@ -1675,14 +1675,14 @@
         <v>2500</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4</v>
+        <v>2.04</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.41</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D14" t="n">
         <v>1135</v>
@@ -1717,10 +1717,10 @@
         <v>1145</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.09</v>
+        <v>5.05</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.18</v>
+        <v>4.13</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>760</v>
+        <v>830</v>
       </c>
       <c r="D15" t="n">
         <v>710</v>
@@ -1759,10 +1759,10 @@
         <v>770</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.32</v>
+        <v>-7.23</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-6.58</v>
+        <v>-14.46</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13525</v>
+        <v>15350</v>
       </c>
       <c r="D16" t="n">
         <v>13550</v>
@@ -1801,14 +1801,14 @@
         <v>14100</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-11.73</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D19" t="n">
         <v>282</v>
@@ -1927,10 +1927,10 @@
         <v>282</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.22</v>
+        <v>6.02</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.22</v>
+        <v>6.02</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>106</v>
@@ -1969,10 +1969,10 @@
         <v>112</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.67</v>
+        <v>1.82</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.93</v>
+        <v>-3.64</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2560</v>
+        <v>2520</v>
       </c>
       <c r="D21" t="n">
         <v>2150</v>
@@ -2011,10 +2011,10 @@
         <v>2580</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.78</v>
+        <v>2.38</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-16.02</v>
+        <v>-14.68</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D24" t="n">
         <v>69</v>
@@ -2137,14 +2137,14 @@
         <v>70</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-1.43</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D25" t="n">
         <v>500</v>
@@ -2179,10 +2179,10 @@
         <v>515</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.91</v>
+        <v>-0.99</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D26" t="n">
         <v>138</v>
@@ -2221,10 +2221,10 @@
         <v>148</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.23</v>
+        <v>6.47</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.82</v>
+        <v>-0.72</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>

--- a/data/performance/daily/signal_list_2026-05-26.xlsx
+++ b/data/performance/daily/signal_list_2026-05-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-26.xlsx
+++ b/data/performance/daily/signal_list_2026-05-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-26.xlsx
+++ b/data/performance/daily/signal_list_2026-05-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-6.67</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -770,15 +801,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -854,15 +895,20 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -896,15 +942,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -938,15 +989,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1020,17 +1081,22 @@
       <c r="G16" s="4" t="n">
         <v>1.81</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1047,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1057,9 +1123,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1089,7 +1156,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1114,15 +1181,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-26.xlsx
+++ b/data/performance/daily/signal_list_2026-05-26.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>2400</v>
       </c>
       <c r="D5" t="n">
+        <v>2430</v>
+      </c>
+      <c r="E5" t="n">
         <v>2350</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2450</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-2.08</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>2300</v>
       </c>
       <c r="D6" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E6" t="n">
         <v>2320</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2330</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>1495</v>
       </c>
       <c r="D7" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E7" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1505</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>6050</v>
       </c>
       <c r="D8" t="n">
+        <v>6050</v>
+      </c>
+      <c r="E8" t="n">
         <v>6075</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>6150</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>75</v>
       </c>
       <c r="D9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E9" t="n">
         <v>70</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>75</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-6.67</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>975</v>
       </c>
       <c r="D10" t="n">
+        <v>990</v>
+      </c>
+      <c r="E10" t="n">
         <v>830</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>990</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-14.87</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>15125</v>
       </c>
       <c r="D11" t="n">
+        <v>15150</v>
+      </c>
+      <c r="E11" t="n">
         <v>15350</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>15500</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>2.48</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>119</v>
       </c>
       <c r="D12" t="n">
+        <v>109</v>
+      </c>
+      <c r="E12" t="n">
         <v>118</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>121</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.68</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.84</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>234</v>
       </c>
       <c r="D13" t="n">
+        <v>234</v>
+      </c>
+      <c r="E13" t="n">
         <v>220</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>238</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-5.98</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>875</v>
       </c>
       <c r="D14" t="n">
+        <v>880</v>
+      </c>
+      <c r="E14" t="n">
         <v>845</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>890</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-3.43</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>310</v>
       </c>
       <c r="D15" t="n">
+        <v>310</v>
+      </c>
+      <c r="E15" t="n">
         <v>308</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>326</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>5.16</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>496</v>
       </c>
       <c r="D16" t="n">
+        <v>498</v>
+      </c>
+      <c r="E16" t="n">
         <v>505</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>510</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>2.82</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>1.81</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1113,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1121,12 +1163,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1156,45 +1199,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
